--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_604_Peru.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_604_Peru.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R8b9c0f31653a4be8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R597d7ffc27214700"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R115fb2560fee42e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R2b50385ad8184c1e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R61cc3510d5d44fbc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R00465d0b6eff400c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R9b609014cfbf44e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R80628caf1cb64f88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R183e9f192bdd42d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R902e9a22f17e4e37"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R506bac20f3fa4944"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R59d40e91dee64e81"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ604CommercialTable" displayName="EEZ604CommercialTable" ref="A1:O12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O12"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ604CommercialTable" displayName="EEZ604CommercialTable" ref="A1:E12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E12"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ604FunctionalTable" displayName="EEZ604FunctionalTable" ref="A1:O23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O23"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ604FunctionalTable" displayName="EEZ604FunctionalTable" ref="A1:E23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E23"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ604ValidationTable" displayName="EEZ604ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ604ValidationTable" displayName="EEZ604ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -8265,7 +8219,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R257507e6b0a94e5b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R27880353d7624c6a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8275,20 +8229,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -8296,660 +8240,231 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>4058512.043144968</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>2.7000067499909353</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>50.11950233545542</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>4058512.043144968</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>50.12070705244467</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$114,A2,'Species'!$U$2:$U$114))</x:f>
-        <x:v>203415493.18328762</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>2.7000067499909353</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>50.11950233545542</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>203410603.8248782</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>4889.358409434557</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0000240368904938</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.000024036890493889593</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>71555.4852102522</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.387089065984055</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2438.3108207735</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>71555.4852102522</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2448.0524153774654</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$114,A3,'Species'!$U$2:$U$114))</x:f>
-        <x:v>175171578.4024644</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.387089065984055</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2438.3108207735</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>174474513.87385607</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>697064.5286083221</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0039952226438773</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.003995222643877347</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>4500.559184173299</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>2.7196262971823937</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>52.435606683085375</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>4500.559184173299</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>54.25877147118261</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$114,A4,'Species'!$U$2:$U$114))</x:f>
-        <x:v>244194.81226659112</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>2.7196262971823937</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>52.435606683085375</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>235989.55123525872</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>8205.261031332397</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0347695946213844</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.034769594621384514</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>1748.5969056653003</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.5743754648709123</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>375.2973215086218</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>1748.5969056653003</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>436.1428925231587</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$114,A5,'Species'!$U$2:$U$114))</x:f>
-        <x:v>762638.112293909</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.5743754648709123</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>375.2973215086218</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>656243.7350944513</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>106394.37719945761</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.1621263129988504</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.16212631299885027</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>5104.9651181068</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.3510207965383607</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>22.43989376434739</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>5104.9651181068</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>40.38683101310791</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$114,A6,'Species'!$U$2:$U$114))</x:f>
-        <x:v>206173.3635527898</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.3510207965383607</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>22.43989376434739</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>114554.87492101571</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>91618.48863177407</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.7997781735167881</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.7997781735167883</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>107366.2491612024</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.0670158059597834</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>11.668520833649543</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>107366.2491612024</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>13.575046896802094</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$114,A7,'Species'!$U$2:$U$114))</x:f>
-        <x:v>1457501.8674970611</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.0670158059597834</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>11.668520833649543</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>1252805.315168298</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>204696.55232876306</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.1633905522673047</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.16339055226730478</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>991866.708425136</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.9602423766852723</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>912.5199682261441</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>991866.708425136</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1138.6763519566994</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$114,A8,'Species'!$U$2:$U$114))</x:f>
-        <x:v>1129415165.1768332</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.9602423766852723</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>912.5199682261441</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>905098177.2566752</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>224316987.9201579</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.2478371888893378</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.24783718888933773</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>572662.2490210724</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.4802782317082332</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>302.1887078946234</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>572662.2490210724</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>616.1856383517436</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$114,A9,'Species'!$U$2:$U$114))</x:f>
-        <x:v>352866253.4729946</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.4802782317082332</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>302.1887078946234</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>173052065.09170693</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>179814188.3812877</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>2.0390756578720817</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>1.0390756578720817</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>661.6979294042</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.5370561836608405</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>344.39448138971835</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>661.6979294042</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>350.4972260247558</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$114,A10,'Species'!$U$2:$U$114))</x:f>
-        <x:v>231923.28872249677</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.5370561836608405</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>344.39448138971835</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>227885.11523380992</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>4038.1734886868508</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0177202161033805</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.017720216103380374</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>25605.3096010619</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.2180579642367055</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>1652.182296298989</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>25605.3096010619</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>2127.8049596485903</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$114,A11,'Species'!$U$2:$U$114))</x:f>
-        <x:v>54483104.76247718</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.2180579642367055</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>1652.182296298989</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>42304639.214129</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>12178465.548348181</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.2878754144836386</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.2878754144836387</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>169169.28513222976</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.46852162800162</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>2941.1801617961423</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>169169.28513222976</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>2949.7336696807884</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$114,A12,'Species'!$U$2:$U$114))</x:f>
-        <x:v>499004336.2303677</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.46852162800162</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>2941.1801617961423</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>497557345.41614926</x:v>
       </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>1446990.8142184615</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0029081890309712</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.002908189030971336</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G12">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O12">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfbb720fe18034661"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9623e92f8ab49d9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8959,20 +8474,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -8980,1254 +8485,440 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>790415.2559603575</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.12628831197491</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1337.4831272560752</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>790415.2559603575</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1362.5606025920686</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$114,A2,'Species'!$U$2:$U$114))</x:f>
-        <x:v>1076988687.4593089</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.12628831197491</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1337.4831272560752</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>1057167068.3727701</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>19821619.08653879</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0187497508005512</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.018749750800551277</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>1024.55</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.2</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1584.893192461114</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>1024.55</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1584.893192461114</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$114,A3,'Species'!$U$2:$U$114))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>1623802.3203360343</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.2</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1584.893192461114</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>1623802.3203360343</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large bathypelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>0.4</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.34</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2187.761623949552</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>0.4</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2187.761623949552</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$114,A4,'Species'!$U$2:$U$114))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>875.1046495798208</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.34</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2187.761623949552</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>875.1046495798208</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>34408.4835347641</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>2.155819296408401</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>14.315921107619918</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>34408.4835347641</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>31.081558556131228</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$114,A5,'Species'!$U$2:$U$114))</x:f>
-        <x:v>1069469.2958134476</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>2.155819296408401</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>14.315921107619918</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>492589.13571652176</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>576880.1600969258</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>2.171118318023385</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>1.1711183180233848</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>132787.76965820638</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.416699829831649</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2610.3565375321355</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>132787.76965820638</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2625.241240271365</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$114,A6,'Species'!$U$2:$U$114))</x:f>
-        <x:v>348599929.110378</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.416699829831649</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2610.3565375321355</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>346623422.63161033</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>1976506.478767693</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0057021722991533</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.005702172299153351</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>2564.2171001916</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.6822250393725398</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>481.08857064747536</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>2564.2171001916</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>490.52608413125</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$114,A7,'Species'!$U$2:$U$114))</x:f>
-        <x:v>1257815.3730193747</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.6822250393725398</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>481.08857064747536</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>1233615.5395609909</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>24199.8334583838</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0196169979076268</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.01961699790762675</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>22624.6801048435</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.291048167064278</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>1954.556221169591</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>22624.6801048435</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>2345.7769731564135</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$114,A8,'Species'!$U$2:$U$114))</x:f>
-        <x:v>53072453.61497192</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.291048167064278</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>1954.556221169591</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>44221209.25089374</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>8851244.364078179</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.200158351931529</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.2001583519315291</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>826.2857724739999</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>2.7343273862915907</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>54.24096235708358</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>826.2857724739999</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>54.340498170563734</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$114,A9,'Species'!$U$2:$U$114))</x:f>
-        <x:v>44900.78050748623</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>2.7343273862915907</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>54.24096235708358</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>44818.53548095596</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>82.24502653027594</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.001835067247238</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.0018350672472379878</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>71555.4852102522</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.387089065984055</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>2438.3108207735</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>71555.4852102522</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>2448.0524153774654</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$114,A10,'Species'!$U$2:$U$114))</x:f>
-        <x:v>175171578.4024644</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.387089065984055</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>2438.3108207735</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>174474513.87385607</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>697064.5286083221</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0039952226438773</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.003995222643877347</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>6035.967738926301</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.5893364272307364</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>388.45116406656723</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>6035.967738926301</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>752.3223808586473</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$114,A11,'Species'!$U$2:$U$114))</x:f>
-        <x:v>4540993.62013502</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.5893364272307364</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>388.45116406656723</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>2344678.694454167</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>2196314.9256808534</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.9367231983110367</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.9367231983110368</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>212999.49851643096</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.3627168251818587</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>230.52436011069074</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>212999.49851643096</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>285.8187579372078</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$114,A12,'Species'!$U$2:$U$114))</x:f>
-        <x:v>60879252.107214436</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.3627168251818587</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>230.52436011069074</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>49101573.09939827</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>11777679.007816166</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.2398635779748672</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.23986357797486735</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>542789.5451377619</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.6230122304622774</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>419.7708052756952</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>542789.5451377619</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>873.1621794453495</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$114,A13,'Species'!$U$2:$U$114))</x:f>
-        <x:v>473943302.212638</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.6230122304622774</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>419.7708052756952</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>227847204.4577066</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>246096097.75493142</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>2.0800926802707917</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>1.0800926802707917</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>611.0264897510001</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.8997599435992036</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>793.8892908865638</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>611.0264897510001</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>824.7351269756225</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$114,A14,'Species'!$U$2:$U$114))</x:f>
-        <x:v>503935.00961025996</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.8997599435992036</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>793.8892908865638</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>485087.38666132774</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>18847.62294893223</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.0388540775686899</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.038854077568689756</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>111936.7991612024</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>2.064279448531085</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>11.595232160430102</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>111936.7991612024</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>13.429072286873796</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$114,A15,'Species'!$U$2:$U$114))</x:f>
-        <x:v>1503207.3674970611</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>2.064279448531085</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>11.595232160430102</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>1297933.1735695794</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>205274.19392748177</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.1581546709087773</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.1581546709087773</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>3674.2734116992997</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>2.716320255576419</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>52.0379591170701</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>3674.2734116992997</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>54.2403924336524</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$114,A16,'Species'!$U$2:$U$114))</x:f>
-        <x:v>199294.0317591049</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>2.716320255576419</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>52.0379591170701</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>191201.68958294584</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>8092.342176159058</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.0423235913542934</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.04232359135429341</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>5.66</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.5899999999999994</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>389.04514499428007</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>5.66</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>389.0451449942804</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$114,A17,'Species'!$U$2:$U$114))</x:f>
-        <x:v>2201.9955206676273</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.5899999999999994</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>389.04514499428007</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>2201.9955206676254</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>1.8189894035458565e-12</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.0000000000000009</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>8.260640798189976e-16</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>240.8</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.7776661129568105</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>599.3301320901525</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>240.8</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>632.9068109650677</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$114,A18,'Species'!$U$2:$U$114))</x:f>
-        <x:v>152403.96008038832</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.7776661129568105</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>599.3301320901525</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>144318.69580730872</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>8085.264273079607</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.056023678899336</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.05602367889933597</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>4072084.841734719</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>2.702787213180693</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>50.441409440098674</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>4072084.841734719</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>53.237590507038945</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$114,A19,'Species'!$U$2:$U$114))</x:f>
-        <x:v>216787985.31419346</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>2.702787213180693</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>50.441409440098674</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>205401698.77676037</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>11386286.537433088</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.0554342374247265</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.055434237424726494</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>2.6</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.4869230769230772</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>306.8478445430767</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>2.6</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>308.3484154732522</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$114,A20,'Species'!$U$2:$U$114))</x:f>
-        <x:v>801.7058802304557</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.4869230769230772</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>306.8478445430767</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>797.8043958119994</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>3.9014844184563344</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.0048902769136605</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.004890276913660563</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>1748.5969056653003</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.5743754648709123</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>375.2973215086218</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>1748.5969056653003</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>436.1428925231587</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$114,A21,'Species'!$U$2:$U$114))</x:f>
-        <x:v>762638.112293909</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.5743754648709123</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>375.2973215086218</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>656243.7350944513</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>106394.37719945761</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.1621263129988504</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.16212631299885027</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>276.5978696945</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.497288020261477</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>314.25921422675657</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>276.5978696945</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>321.50719693184044</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$114,A22,'Species'!$U$2:$U$114))</x:f>
-        <x:v>88928.20576279715</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.497288020261477</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>314.25921422675657</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>86923.42918698837</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>2004.7765758087771</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1.0230637078467777</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0.023063707846777786</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small to medium sharks (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>139.81452633229998</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>3.66</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>457.0881896148752</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>139.81452633229998</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>457.0881896148752</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$114,A23,'Species'!$U$2:$U$114))</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>63907.56872309229</x:v>
       </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>3.66</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>457.0881896148752</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
-        <x:v>63907.56872309229</x:v>
-      </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G23">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O23">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd6f454bdc52a418d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b9ccf90286d455d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10402,7 +9093,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -10501,7 +9192,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>2417258362.672757</x:v>
+        <x:v>1998384823.2690477</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10515,7 +9206,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>2417258362.6727576</x:v>
+        <x:v>2113505685.2717364</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10529,7 +9220,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>-9.5367431640625e-7</x:v>
+        <x:v>-418873539.40371037</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10543,7 +9234,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>-4.76837158203125e-7</x:v>
+        <x:v>-303752677.4010217</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10554,9 +9245,9 @@
         <x:v>EEZ_604</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -10568,47 +9259,19 @@
         <x:v>EEZ_604</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_604</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_604</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reeb207ab72c44148"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf3a4186cdd5a420c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10655,7 +9318,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
